--- a/claim_forms/033_prison_injury_compensation_claim_form--claim_forms.xlsx
+++ b/claim_forms/033_prison_injury_compensation_claim_form--claim_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Incident Reporter</t>
+          <t>Incident Reporter Name</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Relationship to Claimant</t>
+          <t>Incident Reporter Relationship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Relationship to Claimant</t>
+          <t>Incident Reporter Supervisor Relationship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'minor_injuries',_'value':_'minor_injuries'}</t>
+          <t>minor_injuries</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Minor Injuries', 'value': 'minor_injuries'}</t>
+          <t>Minor Injuries</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'serious_injuries',_'value':_'serious_injuries'}</t>
+          <t>serious_injuries</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Serious Injuries', 'value': 'serious_injuries'}</t>
+          <t>Serious Injuries</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'both_minor_and_serious_injuries',_'value':_'both_injuries'}</t>
+          <t>both_minor_and_serious_injuries</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Both Minor and Serious Injuries', 'value': 'both_injuries'}</t>
+          <t>Both Minor and Serious Injuries</t>
         </is>
       </c>
     </row>
